--- a/data/trans_orig/P33B2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33B2_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que se despierta durante la noche y tiene dificultad en volver a dormirse en 2023</t>
+          <t>Población según la frecuencia con la que se despierta durante la noche y tiene dificultad en volver a dormirse en 2023 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23817</t>
+          <t>23800</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23886</t>
+          <t>24088</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33419</t>
+          <t>37136</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>22280</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4962</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23882</t>
+          <t>23983</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10008</t>
+          <t>10939</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35406</t>
+          <t>37747</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17908</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54837</t>
+          <t>54809</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17193</t>
+          <t>16766</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46830</t>
+          <t>48424</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38725</t>
+          <t>40808</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>85668</t>
+          <t>88693</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>328388</t>
+          <t>328918</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>370867</t>
+          <t>372533</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>238898</t>
+          <t>242254</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>277702</t>
+          <t>279508</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>588658</t>
+          <t>582960</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>642176</t>
+          <t>640844</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,86%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18013</t>
+          <t>17356</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9415</t>
+          <t>9689</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28851</t>
+          <t>30374</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>15590</t>
+          <t>16937</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>39812</t>
+          <t>40385</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9500</t>
+          <t>9225</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32607</t>
+          <t>31433</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11821</t>
+          <t>11969</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35223</t>
+          <t>32862</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25526</t>
+          <t>26455</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57192</t>
+          <t>58742</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31356</t>
+          <t>31187</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60921</t>
+          <t>60545</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47064</t>
+          <t>48638</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>94991</t>
+          <t>96022</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89160</t>
+          <t>90249</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>143618</t>
+          <t>143524</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>332440</t>
+          <t>334195</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>368903</t>
+          <t>372199</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>371586</t>
+          <t>370150</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>437644</t>
+          <t>439844</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>719253</t>
+          <t>716873</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>795513</t>
+          <t>791806</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,68%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17122</t>
+          <t>17153</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39250</t>
+          <t>38026</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25868</t>
+          <t>26244</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43989</t>
+          <t>45042</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47294</t>
+          <t>45753</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75140</t>
+          <t>75288</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23159</t>
+          <t>22913</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47478</t>
+          <t>46330</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36486</t>
+          <t>36072</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59433</t>
+          <t>56759</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>64672</t>
+          <t>63512</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>97258</t>
+          <t>97665</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65357</t>
+          <t>67208</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98407</t>
+          <t>99851</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>103592</t>
+          <t>103252</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>135393</t>
+          <t>133872</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>177024</t>
+          <t>178002</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>221572</t>
+          <t>223449</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>371633</t>
+          <t>372032</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>414173</t>
+          <t>414099</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>324440</t>
+          <t>325442</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>362214</t>
+          <t>362378</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>709437</t>
+          <t>710303</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>765749</t>
+          <t>767922</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>71,18%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14635</t>
+          <t>13948</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56494</t>
+          <t>57342</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46841</t>
+          <t>46953</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72569</t>
+          <t>72821</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>57773</t>
+          <t>58760</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>120882</t>
+          <t>121554</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24883</t>
+          <t>25374</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>89165</t>
+          <t>88017</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>74293</t>
+          <t>74535</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>106940</t>
+          <t>108806</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>86744</t>
+          <t>90720</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>186334</t>
+          <t>186319</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>55384</t>
+          <t>54781</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>190781</t>
+          <t>193132</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>144023</t>
+          <t>144858</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>189934</t>
+          <t>192229</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>181166</t>
+          <t>191109</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>366315</t>
+          <t>371207</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>564406</t>
+          <t>566039</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>789497</t>
+          <t>791269</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>365437</t>
+          <t>364110</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>440916</t>
+          <t>448854</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>938511</t>
+          <t>935966</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1279243</t>
+          <t>1256803</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>78,54%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>42761</t>
+          <t>43899</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>70061</t>
+          <t>67965</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>62050</t>
+          <t>61357</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>87435</t>
+          <t>85302</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>111488</t>
+          <t>110534</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>145152</t>
+          <t>146621</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>35411</t>
+          <t>34100</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>58708</t>
+          <t>59710</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>87400</t>
+          <t>87740</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>114481</t>
+          <t>115470</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>128380</t>
+          <t>127731</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>164553</t>
+          <t>163422</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>118116</t>
+          <t>116703</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>154677</t>
+          <t>155082</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>136920</t>
+          <t>136801</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>165859</t>
+          <t>166980</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>261301</t>
+          <t>263512</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>310636</t>
+          <t>310411</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>302272</t>
+          <t>302733</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>346242</t>
+          <t>346212</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>204736</t>
+          <t>202469</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>239075</t>
+          <t>236401</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>517213</t>
+          <t>516934</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>575156</t>
+          <t>570472</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,61%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>27439</t>
+          <t>26844</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>44063</t>
+          <t>45109</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22439</t>
+          <t>26882</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>95979</t>
+          <t>97101</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>49794</t>
+          <t>53273</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>128237</t>
+          <t>129623</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31473</t>
+          <t>31049</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>50361</t>
+          <t>50557</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>28008</t>
+          <t>28598</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>104742</t>
+          <t>105106</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>57738</t>
+          <t>53925</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>140297</t>
+          <t>142127</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>78777</t>
+          <t>78262</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>104935</t>
+          <t>104550</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>162152</t>
+          <t>160643</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>486618</t>
+          <t>473229</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>250018</t>
+          <t>248810</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>662719</t>
+          <t>672713</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>68,89%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>186400</t>
+          <t>187332</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>217875</t>
+          <t>217195</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>70713</t>
+          <t>76475</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>255977</t>
+          <t>255775</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>203264</t>
+          <t>192774</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>471404</t>
+          <t>471408</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>30671</t>
+          <t>31909</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>49508</t>
+          <t>50331</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>64458</t>
+          <t>63475</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>87622</t>
+          <t>86992</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>101299</t>
+          <t>101979</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>131230</t>
+          <t>131160</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>32102</t>
+          <t>33009</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>50706</t>
+          <t>51792</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>69021</t>
+          <t>69548</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>92211</t>
+          <t>92286</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>106271</t>
+          <t>106823</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>136654</t>
+          <t>136339</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>63849</t>
+          <t>64138</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>87163</t>
+          <t>87979</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>120332</t>
+          <t>120594</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>146567</t>
+          <t>146058</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>190906</t>
+          <t>189526</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>225002</t>
+          <t>226149</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>113062</t>
+          <t>113452</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>139178</t>
+          <t>138236</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>123777</t>
+          <t>123102</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>151356</t>
+          <t>150827</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>244028</t>
+          <t>242678</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>282947</t>
+          <t>281051</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,66%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>164450</t>
+          <t>164739</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>240846</t>
+          <t>241932</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>272533</t>
+          <t>263960</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>368388</t>
+          <t>369815</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>464362</t>
+          <t>471457</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>591541</t>
+          <t>596950</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>191402</t>
+          <t>193285</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>282418</t>
+          <t>279149</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>338174</t>
+          <t>342095</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>458051</t>
+          <t>464038</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>577240</t>
+          <t>585885</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>722211</t>
+          <t>726489</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>446576</t>
+          <t>455661</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>648589</t>
+          <t>656590</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>817813</t>
+          <t>818927</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1480652</t>
+          <t>1552193</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1365154</t>
+          <t>1375464</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2119739</t>
+          <t>2165804</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2316502</t>
+          <t>2315878</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2669232</t>
+          <t>2660483</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1552200</t>
+          <t>1531210</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2061828</t>
+          <t>2059356</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3943748</t>
+          <t>3957080</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4594389</t>
+          <t>4592467</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,52%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33B2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33B2_2023-Edad-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23800</t>
+          <t>21292</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9762</t>
+          <t>15689</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>6461</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24088</t>
+          <t>31256</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>15962</t>
+          <t>21051</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6319</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37136</t>
+          <t>40715</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8772</t>
+          <t>10855</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22280</t>
+          <t>28785</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11956</t>
+          <t>14935</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>6357</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23983</t>
+          <t>27287</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>20727</t>
+          <t>25790</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10939</t>
+          <t>13741</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37747</t>
+          <t>44098</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31028</t>
+          <t>31994</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>18842</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54809</t>
+          <t>53568</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29081</t>
+          <t>34116</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16766</t>
+          <t>21441</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48424</t>
+          <t>55789</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>60109</t>
+          <t>66110</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>40808</t>
+          <t>46336</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>88693</t>
+          <t>91382</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>353987</t>
+          <t>359581</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>328918</t>
+          <t>335265</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>372533</t>
+          <t>377419</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>262401</t>
+          <t>297773</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>242254</t>
+          <t>274048</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>279508</t>
+          <t>314956</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>616389</t>
+          <t>657354</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>582960</t>
+          <t>623631</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>640844</t>
+          <t>681863</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>88,52%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8409</t>
+          <t>10773</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17356</t>
+          <t>20921</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18034</t>
+          <t>18741</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9689</t>
+          <t>11482</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30374</t>
+          <t>29204</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>26443</t>
+          <t>29514</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16937</t>
+          <t>18733</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>40385</t>
+          <t>43579</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18142</t>
+          <t>17756</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9225</t>
+          <t>9479</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31433</t>
+          <t>30572</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21161</t>
+          <t>23346</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11969</t>
+          <t>15128</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32862</t>
+          <t>35574</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,17 +1477,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>39303</t>
+          <t>41102</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26455</t>
+          <t>28753</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58742</t>
+          <t>58966</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44269</t>
+          <t>53160</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31187</t>
+          <t>37918</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60545</t>
+          <t>73142</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>74462</t>
+          <t>89139</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48638</t>
+          <t>70940</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96022</t>
+          <t>106682</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>118731</t>
+          <t>142299</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>90249</t>
+          <t>120151</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>143524</t>
+          <t>170573</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>352727</t>
+          <t>395201</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>334195</t>
+          <t>373097</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>372199</t>
+          <t>413965</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>397846</t>
+          <t>369857</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>370150</t>
+          <t>348786</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>439844</t>
+          <t>389771</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>750574</t>
+          <t>765058</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>716873</t>
+          <t>733754</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>791806</t>
+          <t>790806</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>80,86%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>26280</t>
+          <t>28382</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17153</t>
+          <t>18188</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38026</t>
+          <t>43027</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>34274</t>
+          <t>41288</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26244</t>
+          <t>30911</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45042</t>
+          <t>52320</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,17 +1933,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>60555</t>
+          <t>69670</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45753</t>
+          <t>55196</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75288</t>
+          <t>86699</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33640</t>
+          <t>35748</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25124</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46330</t>
+          <t>50442</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>45621</t>
+          <t>53493</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36072</t>
+          <t>42087</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56759</t>
+          <t>67532</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>79261</t>
+          <t>89242</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>63512</t>
+          <t>72607</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>97665</t>
+          <t>107099</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>81432</t>
+          <t>94773</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>67208</t>
+          <t>76997</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99851</t>
+          <t>112080</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>118623</t>
+          <t>133520</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>103252</t>
+          <t>115773</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>133872</t>
+          <t>149984</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>200055</t>
+          <t>228294</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>178002</t>
+          <t>203707</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>223449</t>
+          <t>257514</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>394985</t>
+          <t>461933</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>372032</t>
+          <t>439943</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>414099</t>
+          <t>485932</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>343950</t>
+          <t>393838</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>325442</t>
+          <t>375159</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>362378</t>
+          <t>415256</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>738935</t>
+          <t>855771</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>710303</t>
+          <t>826677</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>767922</t>
+          <t>888608</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,49%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>36167</t>
+          <t>42171</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>30436</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>57342</t>
+          <t>57515</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>59537</t>
+          <t>66271</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46953</t>
+          <t>54339</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72821</t>
+          <t>80073</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>95704</t>
+          <t>108442</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58760</t>
+          <t>91082</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>121554</t>
+          <t>128561</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>57566</t>
+          <t>60950</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25374</t>
+          <t>48725</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>88017</t>
+          <t>79650</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,27 +2580,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>91670</t>
+          <t>98110</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>74535</t>
+          <t>83394</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>108806</t>
+          <t>112463</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>149237</t>
+          <t>159060</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>90720</t>
+          <t>140531</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>186319</t>
+          <t>185291</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>130658</t>
+          <t>142932</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>54781</t>
+          <t>121901</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>193132</t>
+          <t>164578</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>171308</t>
+          <t>188213</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>144858</t>
+          <t>170715</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>192229</t>
+          <t>207920</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>301967</t>
+          <t>331145</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>191109</t>
+          <t>302364</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>371207</t>
+          <t>359631</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>663395</t>
+          <t>454564</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>566039</t>
+          <t>428036</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>791269</t>
+          <t>478163</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>389982</t>
+          <t>383901</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>364110</t>
+          <t>362921</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>448854</t>
+          <t>407138</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1053378</t>
+          <t>838465</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>935966</t>
+          <t>802841</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1256803</t>
+          <t>871466</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>60,64%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>55145</t>
+          <t>58255</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>43899</t>
+          <t>45922</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67965</t>
+          <t>73614</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>72962</t>
+          <t>82058</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>61357</t>
+          <t>70012</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>85302</t>
+          <t>97294</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>128107</t>
+          <t>140314</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>110534</t>
+          <t>122747</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>146621</t>
+          <t>161774</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>45590</t>
+          <t>47610</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34100</t>
+          <t>36089</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>59710</t>
+          <t>62070</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>100304</t>
+          <t>114215</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>87740</t>
+          <t>98642</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>115470</t>
+          <t>127955</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>145893</t>
+          <t>161825</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>127731</t>
+          <t>143785</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>163422</t>
+          <t>182288</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>135030</t>
+          <t>151955</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>116703</t>
+          <t>132540</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>155082</t>
+          <t>175265</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>151657</t>
+          <t>166667</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>136801</t>
+          <t>150008</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>166980</t>
+          <t>184577</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>286687</t>
+          <t>318622</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>263512</t>
+          <t>293690</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>310411</t>
+          <t>344442</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,33%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>324439</t>
+          <t>350444</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>302733</t>
+          <t>327828</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>346212</t>
+          <t>373340</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>220140</t>
+          <t>244654</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>202469</t>
+          <t>225558</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>236401</t>
+          <t>262774</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>544579</t>
+          <t>595098</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>516934</t>
+          <t>566908</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>570472</t>
+          <t>623829</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,31%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>560204</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>545063</t>
+          <t>607594</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>545063</t>
+          <t>607594</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>545063</t>
+          <t>607594</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1105267</t>
+          <t>1215858</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1105267</t>
+          <t>1215858</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1105267</t>
+          <t>1215858</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>35471</t>
+          <t>39566</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26844</t>
+          <t>30262</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>45109</t>
+          <t>49683</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>61128</t>
+          <t>68083</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>26882</t>
+          <t>57881</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>97101</t>
+          <t>78744</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>96599</t>
+          <t>107648</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>53273</t>
+          <t>93717</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>129623</t>
+          <t>123767</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>40634</t>
+          <t>44226</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31049</t>
+          <t>35003</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>50557</t>
+          <t>55483</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>65833</t>
+          <t>72305</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>28598</t>
+          <t>60994</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>105106</t>
+          <t>83432</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>106467</t>
+          <t>116531</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>53925</t>
+          <t>102159</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>142127</t>
+          <t>133221</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>91350</t>
+          <t>101507</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>78262</t>
+          <t>87855</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>104550</t>
+          <t>117841</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>315806</t>
+          <t>119882</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>160643</t>
+          <t>105824</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>473229</t>
+          <t>133079</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>407156</t>
+          <t>221389</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>248810</t>
+          <t>202965</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>672713</t>
+          <t>242105</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>28,61%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>200710</t>
+          <t>221782</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>187332</t>
+          <t>204267</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>217195</t>
+          <t>237226</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>165600</t>
+          <t>178896</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>76475</t>
+          <t>164979</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>255775</t>
+          <t>195587</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>366310</t>
+          <t>400678</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>192774</t>
+          <t>374860</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>471408</t>
+          <t>422377</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>49,91%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>40317</t>
+          <t>45359</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>31909</t>
+          <t>36479</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>50331</t>
+          <t>57200</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>75517</t>
+          <t>85054</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>63475</t>
+          <t>73394</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>86992</t>
+          <t>99345</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>115834</t>
+          <t>130413</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>101979</t>
+          <t>113627</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>131160</t>
+          <t>146928</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,96%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>41462</t>
+          <t>45706</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>33009</t>
+          <t>36474</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>51792</t>
+          <t>56216</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>80165</t>
+          <t>86686</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>69548</t>
+          <t>75068</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>92286</t>
+          <t>99207</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>121627</t>
+          <t>132392</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>106823</t>
+          <t>117849</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>136339</t>
+          <t>150397</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>75299</t>
+          <t>84151</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>64138</t>
+          <t>71455</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>87979</t>
+          <t>97206</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>133023</t>
+          <t>142755</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>120594</t>
+          <t>127023</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>146058</t>
+          <t>155498</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>208322</t>
+          <t>226906</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>189526</t>
+          <t>206851</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>226149</t>
+          <t>245190</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,65%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>125680</t>
+          <t>134982</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>113452</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>138236</t>
+          <t>150124</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>137126</t>
+          <t>150114</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>123102</t>
+          <t>134726</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>150827</t>
+          <t>165484</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>262806</t>
+          <t>285096</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>242678</t>
+          <t>263974</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>281051</t>
+          <t>304528</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,3%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>207989</t>
+          <t>229868</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>164739</t>
+          <t>200258</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>241932</t>
+          <t>257390</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>331214</t>
+          <t>377184</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>263960</t>
+          <t>349499</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>369815</t>
+          <t>407118</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>539203</t>
+          <t>607052</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>471457</t>
+          <t>568166</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>596950</t>
+          <t>653772</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>245807</t>
+          <t>262852</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>193285</t>
+          <t>231205</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>279149</t>
+          <t>295881</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>416710</t>
+          <t>463090</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>342095</t>
+          <t>430619</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>464038</t>
+          <t>498257</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>662517</t>
+          <t>725942</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>585885</t>
+          <t>682668</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>726489</t>
+          <t>772046</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>589067</t>
+          <t>660472</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>455661</t>
+          <t>615675</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>656590</t>
+          <t>709661</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>993961</t>
+          <t>874292</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>818927</t>
+          <t>832242</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1552193</t>
+          <t>918950</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1583027</t>
+          <t>1534764</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1375464</t>
+          <t>1473557</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>2165804</t>
+          <t>1606054</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>2415925</t>
+          <t>2378487</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2315878</t>
+          <t>2321435</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2660483</t>
+          <t>2433625</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>1917047</t>
+          <t>2019033</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1531210</t>
+          <t>1967762</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2059356</t>
+          <t>2071888</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>4332971</t>
+          <t>4397520</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3957080</t>
+          <t>4314385</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4592467</t>
+          <t>4478098</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>61,64%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3658932</t>
+          <t>3733598</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3658932</t>
+          <t>3733598</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3658932</t>
+          <t>3733598</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>7117719</t>
+          <t>7265279</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7117719</t>
+          <t>7265279</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7117719</t>
+          <t>7265279</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
